--- a/Dataset/1_label/UP_DOWN_UP-DOWN_V2_10 divisions_per_second.xlsx
+++ b/Dataset/1_label/UP_DOWN_UP-DOWN_V2_10 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3654,6 +3654,42 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>UP_DOWN_UP-DOWN_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>37200</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>UP_DOWN_UP-DOWN_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>37400</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
